--- a/fixtures/idea_exports/SoD Violation Entries.xlsx
+++ b/fixtures/idea_exports/SoD Violation Entries.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>931</v>
+        <v>1066</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45674</v>
+        <v>45677</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -493,50 +493,50 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>20000</v>
+        <v>45520.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1378</v>
+        <v>1262</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45683</v>
+        <v>45680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Suspense Account 8</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -544,87 +544,87 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1803</v>
+        <v>1897</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45689</v>
+        <v>45692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>14787.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1804</v>
+        <v>1918</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45689</v>
+        <v>45692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Suspense Account 33</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>54999</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1925</v>
+        <v>2312</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45692</v>
+        <v>45700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Suspense Account 14</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -638,143 +638,143 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>31177.22</v>
       </c>
       <c r="H6" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2495</v>
+        <v>3348</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45702</v>
+        <v>45720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Suspense Account 9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>110999</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>87999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2915</v>
+        <v>3377</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45711</v>
+        <v>45720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Consultancy fee (related party)</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>29999</v>
+        <v>36394.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3383</v>
+        <v>4347</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45720</v>
+        <v>45738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Adjustment per director</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>23092.59</v>
+        <v>29999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4026</v>
+        <v>5056</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45731</v>
+        <v>45751</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Suspense Account 21</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Cash advance, no invoice</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -782,14 +782,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4665</v>
+        <v>5465</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45744</v>
+        <v>45759</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travel Expense</t>
+          <t>Suspense Account 45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -799,16 +799,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>80000</v>
+        <v>75370.53</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -816,33 +816,33 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5480</v>
+        <v>5807</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45760</v>
+        <v>45765</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VAT Payable</t>
+          <t>Suspense Account 46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Adjustment per director</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>138999</v>
+        <v>14999</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -850,53 +850,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5816</v>
+        <v>5842</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45765</v>
+        <v>45767</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VAT Payable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>19062.6</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>28948.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6019</v>
+        <v>6010</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Suspense Account 36</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -913,24 +913,24 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>170000</v>
+        <v>23092.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6609</v>
+        <v>6202</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45781</v>
+        <v>45774</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Adjustment per director</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -944,56 +944,56 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7836</v>
+        <v>7965</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45803</v>
+        <v>45805</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VAT Payable</t>
+          <t>Suspense Account 44</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Adjustment per director</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>31224.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7950</v>
+        <v>8627</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45805</v>
+        <v>45818</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Suspense Account 1</t>
+          <t>Suspense Account 37</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1003,152 +1003,152 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>58265.84</v>
+        <v>170000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7978</v>
+        <v>8917</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45805</v>
+        <v>45821</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Suspense Account 44</t>
+          <t>Suspense Account 42</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Correction entry - reversal</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>70999</v>
       </c>
       <c r="H18" t="n">
-        <v>32940.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8242</v>
+        <v>9364</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45811</v>
+        <v>45830</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Suspense Account 34</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>31177.22</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>27999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>8640</v>
+        <v>9393</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45818</v>
+        <v>45831</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Suspense Account 16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>105792.85</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9583</v>
+        <v>10027</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45833</v>
+        <v>45841</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Suspense Account 12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Cash advance, no invoice</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>68345.99000000001</v>
+        <v>33840.53</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1156,48 +1156,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10136</v>
+        <v>10874</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45843</v>
+        <v>45856</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Consultancy fee (related party)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>25999</v>
       </c>
       <c r="H22" t="n">
-        <v>159097.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11125</v>
+        <v>10892</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45861</v>
+        <v>45858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Suspense Account 13</t>
+          <t>Suspense Account 11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1207,50 +1207,50 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>10999</v>
+        <v>23911.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11675</v>
+        <v>11254</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45870</v>
+        <v>45863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Suspense Account 29</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>22999</v>
+        <v>97999</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1258,203 +1258,203 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11691</v>
+        <v>12854</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45872</v>
+        <v>45894</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Suspense Account 24</t>
+          <t>Suspense Account 19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Cash advance, no invoice</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>11856</v>
+        <v>13691</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45875</v>
+        <v>45908</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Correction entry - reversal</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>11294.49</v>
       </c>
       <c r="H26" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>12084</v>
+        <v>14858</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45878</v>
+        <v>45930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>42022.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>12318</v>
+        <v>15344</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45883</v>
+        <v>45938</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suspense Account 1</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>24999</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>44293.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12811</v>
+        <v>15503</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45893</v>
+        <v>45940</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>149908.32</v>
       </c>
       <c r="H29" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>12951</v>
+        <v>15568</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45895</v>
+        <v>45942</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Suspense Account 14</t>
+          <t>Suspense Account 20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>130000</v>
+        <v>19999</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1462,78 +1462,78 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13649</v>
+        <v>15623</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45906</v>
+        <v>45943</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Suspense Account 19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>31308.86</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>62228.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13700</v>
+        <v>15953</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45908</v>
+        <v>45949</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="H32" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14210</v>
+        <v>16348</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45917</v>
+        <v>45955</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1542,70 +1542,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Director fees</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="H33" t="n">
-        <v>30534.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>14703</v>
+        <v>16775</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45925</v>
+        <v>45962</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Suspense Account 4</t>
+          <t>VAT Payable</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>64643.66</v>
       </c>
       <c r="H34" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>15351</v>
+        <v>17133</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45938</v>
+        <v>45968</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Suspense Account 8</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1615,36 +1615,36 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>13101.57</v>
+        <v>63999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>15510</v>
+        <v>17578</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45940</v>
+        <v>45976</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Suspense Account 28</t>
+          <t>Suspense Account 48</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Adjustment per director</t>
+          <t>Consultancy fee (related party)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1658,56 +1658,56 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>23999</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>26875.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>15765</v>
+        <v>17799</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45945</v>
+        <v>45981</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Suspense Account 29</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>22999</v>
       </c>
       <c r="H37" t="n">
-        <v>36394.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>16359</v>
+        <v>18677</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45955</v>
+        <v>45996</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Suspense Account 26</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1717,36 +1717,36 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>9141.09</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>16399</v>
+        <v>18871</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45957</v>
+        <v>46001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Suspense Account 7</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Correction entry - reversal</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1763,279 +1763,75 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>41049.01</v>
+        <v>9614.950000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>17866</v>
+        <v>19431</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45982</v>
+        <v>46011</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Suspense Account 5</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>71470.53999999999</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>17946</v>
+        <v>19756</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45983</v>
+        <v>46017</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Travel Expense</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>17954</v>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45984</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Customer receipt</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>user_d</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>user_d</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>105055.78</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>18409</v>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>45993</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Cost of Sales</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Purchase invoice</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>user_c</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>user_c</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>23139.69</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>18651</v>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>45996</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Cost of Sales</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Staff travel claim</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>user_a</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>user_a</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>18999</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>18686</v>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>45997</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Suspense Account 3</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Utility bill</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>user_e</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>user_e</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>27999</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>19432</v>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>46011</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Supplier payment</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>user_a</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>user_a</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>19756</v>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>46017</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Cost of Sales</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Purchase invoice</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>user_b</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>user_b</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>24641.62</v>
+        <v>33965.61</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/idea_exports/SoD Violation Entries.xlsx
+++ b/fixtures/idea_exports/SoD Violation Entries.xlsx
@@ -1564,7 +1564,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16775</v>
+        <v>16774</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>45962</v>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17578</v>
+        <v>17576</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>45976</v>
